--- a/cashier/收银合规分析_20260810.xlsx
+++ b/cashier/收银合规分析_20260810.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3,278</t>
+          <t>3,279</t>
         </is>
       </c>
     </row>
@@ -695,27 +695,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海中庚漫游城授权体验店</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>LSD2026080800943589</t>
+          <t>LSD2026080100898820</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>150****1153</t>
+          <t>150****6552</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -752,27 +752,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>LSD2026080800943352</t>
+          <t>LSD2026080100901233</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>185****6616</t>
+          <t>177****0229</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -809,27 +809,27 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LSD2026080800943068</t>
+          <t>LSD2026080100898061</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>187****2309</t>
+          <t>158****7998</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -866,27 +866,27 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LSD2026080800942903</t>
+          <t>LSD2026080100895600</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -906,7 +906,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>158****3037</t>
+          <t>135****5494</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -923,27 +923,27 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海复地活力城授权体验店</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LSD2026080800938677</t>
+          <t>LSD2026080100894959</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>152****6596</t>
+          <t>135****5494</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -980,27 +980,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>LSD2026080800937682</t>
+          <t>LSD2026080100901441</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>177****0313</t>
+          <t>186****9677</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1037,27 +1037,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>LSD2026080800937314</t>
+          <t>LSD2026080100899458</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1077,7 +1077,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>136****4038</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1094,27 +1094,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>LSD2026080900951481</t>
+          <t>LSD2026080100896886</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>139****1145</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1151,27 +1151,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>上海爱飞</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>LSD2026080900947256</t>
+          <t>LSD2026080100898888</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>153****8548</t>
+          <t>188****7855</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>DJI上海中庚漫游城授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>LSD2026080100898820</t>
+          <t>LSD2026080100898806</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>150****6552</t>
+          <t>188****7855</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1280,12 +1280,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>LSD2026080100901233</t>
+          <t>LSD2026080100898731</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>177****0229</t>
+          <t>188****7855</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1322,12 +1322,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>LSD2026080100898061</t>
+          <t>LSD2026080200903412</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>158****7998</t>
+          <t>137****9080</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1379,12 +1379,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1394,12 +1394,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海百联又一城授权体验店</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>LSD2026080100895600</t>
+          <t>LSD2026080300911904</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>177****3777</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1436,12 +1436,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DJI上海复地活力城授权体验店</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>LSD2026080100894959</t>
+          <t>LSD2026080300911587</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>135****5494</t>
+          <t>138****4526</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1493,12 +1493,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1508,12 +1508,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>LSD2026080100901441</t>
+          <t>LSD2026080400915298</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1533,7 +1533,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>186****9677</t>
+          <t>138****5533</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1550,7 +1550,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>LSD2026080100899458</t>
+          <t>LSD2026080400917951</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1607,12 +1607,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1622,12 +1622,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>LSD2026080100896886</t>
+          <t>LSD2026080400917906</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1664,12 +1664,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>LSD2026080100898888</t>
+          <t>LSD2026080500924466</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>185****5918</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1721,12 +1721,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1736,12 +1736,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>LSD2026080100898806</t>
+          <t>LSD2026080500923088</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1761,7 +1761,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>185****5918</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1778,12 +1778,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>LSD2026080100898731</t>
+          <t>LSD2026080500923845</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>188****7855</t>
+          <t>188****3772</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1835,12 +1835,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海漕河泾印象城授权体验店</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海漕河泾印象城授权体验店</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>LSD2026080200903412</t>
+          <t>LSD2026080500922902</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>137****9080</t>
+          <t>183****5937</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1892,12 +1892,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DJI上海百联又一城授权体验店</t>
+          <t>DJI上海长宁龙之梦授权体验店</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>LSD2026080300911904</t>
+          <t>LSD2026080500923260</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1949,12 +1949,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1964,12 +1964,12 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>LSD2026080300911587</t>
+          <t>LSD2026080500922161</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1989,7 +1989,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>138****4526</t>
+          <t>189****1806</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2006,12 +2006,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海静安大融城授权体验店</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2021,12 +2021,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海静安大融城授权体验店</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>LSD2026080400915298</t>
+          <t>LSD2026080500923624</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>138****5533</t>
+          <t>139****1884</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2063,12 +2063,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2078,12 +2078,12 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI上海世博天地授权体验店</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>LSD2026080400917951</t>
+          <t>LSD2026080600925154</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>189****6007</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2120,12 +2120,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>LSD2026080400917906</t>
+          <t>LSD2026080600925259</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>167****1142</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2177,12 +2177,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2192,12 +2192,12 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>LSD2026080500924466</t>
+          <t>LSD2026080700936141</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -2217,7 +2217,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>185****5918</t>
+          <t>186****8771</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2234,12 +2234,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海美罗城授权体验店</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>LSD2026080500923088</t>
+          <t>LSD2026080700935174</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -2274,7 +2274,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>185****5918</t>
+          <t>130****8432</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2291,12 +2291,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2306,12 +2306,12 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海长泰广场授权体验店</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>LSD2026080500923845</t>
+          <t>LSD2026080700931362</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2331,7 +2331,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>188****3772</t>
+          <t>186****7655</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2348,12 +2348,12 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DJI上海漕河泾印象城授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2363,12 +2363,12 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>DJI上海漕河泾印象城授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>LSD2026080500922902</t>
+          <t>LSD2026080800943589</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>183****5937</t>
+          <t>150****1153</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2405,12 +2405,12 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2420,12 +2420,12 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>DJI上海长宁龙之梦授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>LSD2026080500923260</t>
+          <t>LSD2026080800943352</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>177****3777</t>
+          <t>185****6616</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2462,12 +2462,12 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2477,12 +2477,12 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>LSD2026080500922161</t>
+          <t>LSD2026080800943068</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2502,7 +2502,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>189****1806</t>
+          <t>187****2309</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2519,12 +2519,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DJI上海静安大融城授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>DJI上海静安大融城授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>LSD2026080500923624</t>
+          <t>LSD2026080800942903</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2559,7 +2559,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>139****1884</t>
+          <t>158****3037</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -2576,12 +2576,12 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>DJI上海世博天地授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>LSD2026080600925154</t>
+          <t>LSD2026080800938677</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>189****6007</t>
+          <t>152****6596</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2633,12 +2633,12 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2648,12 +2648,12 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>LSD2026080600925259</t>
+          <t>LSD2026080800937682</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>167****1142</t>
+          <t>177****0313</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -2690,12 +2690,12 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>LSD2026080700936141</t>
+          <t>LSD2026080800937314</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>186****8771</t>
+          <t>136****4038</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -2747,12 +2747,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>DJI上海美罗城授权体验店</t>
+          <t>DJI上海天荟广场授权体验店</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>LSD2026080700935174</t>
+          <t>LSD2026080800940954</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2787,7 +2787,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>130****8432</t>
+          <t>135****9693</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -2804,12 +2804,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2819,12 +2819,12 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>DJI上海长泰广场授权体验店</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>LSD2026080700931362</t>
+          <t>LSD2026080800939689</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>186****7655</t>
+          <t>150****0165</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>DJI上海天荟广场授权体验店</t>
+          <t>DJI上海江桥万达授权体验店</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>LSD2026080800940954</t>
+          <t>LSD2026080800939622</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>135****9693</t>
+          <t>150****0165</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -2938,7 +2938,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>LSD2026080800939689</t>
+          <t>LSD2026080800939401</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2980,7 +2980,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2990,12 +2990,12 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>LSD2026080800939622</t>
+          <t>LSD2026080800942684</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3015,7 +3015,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>150****0165</t>
+          <t>131****7661</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3032,12 +3032,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3047,12 +3047,12 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>DJI上海江桥万达授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>LSD2026080800939401</t>
+          <t>LSD2026080900951481</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>150****0165</t>
+          <t>139****1145</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3089,12 +3089,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3104,12 +3104,12 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>DJI上海陆家嘴中心L+mall授权体验店</t>
+          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>LSD2026080800942684</t>
+          <t>LSD2026080900947256</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>131****7661</t>
+          <t>153****8548</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -32116,7 +32116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32300,17 +32300,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>38.1%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2,072</t>
+          <t>2,081</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -32320,12 +32320,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>45</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>98.17%</t>
+          <t>97.72%</t>
         </is>
       </c>
     </row>
@@ -32374,82 +32374,40 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DJI上海LCM置汇旭辉广场授权体验店</t>
+          <t>福建易联</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3,367</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3,171</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>福建易联</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>80.0%</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>3,367</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3,171</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
         <is>
           <t>99.84%</t>
         </is>
